--- a/stacked_model/results/baseline/baseline_stacked_top10.xlsx
+++ b/stacked_model/results/baseline/baseline_stacked_top10.xlsx
@@ -507,19 +507,19 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>3.054853077716411</v>
+        <v>3.054853077716398</v>
       </c>
       <c r="H2" t="n">
         <v>4.911296439845443</v>
       </c>
       <c r="I2" t="n">
-        <v>90.6398084036133</v>
+        <v>90.63981244359209</v>
       </c>
       <c r="J2" t="n">
-        <v>6.124067204543739</v>
+        <v>5.958147515790889</v>
       </c>
       <c r="K2" t="n">
-        <v>0.908635064160345</v>
+        <v>0.9066673444051729</v>
       </c>
     </row>
     <row r="3">
@@ -544,19 +544,19 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>2.796265769646185</v>
+        <v>2.796265769646167</v>
       </c>
       <c r="H3" t="n">
-        <v>5.842139841967368</v>
+        <v>5.842139841967365</v>
       </c>
       <c r="I3" t="n">
-        <v>89.75866628974364</v>
+        <v>89.75865251071539</v>
       </c>
       <c r="J3" t="n">
-        <v>7.659917675053562</v>
+        <v>7.527948010341123</v>
       </c>
       <c r="K3" t="n">
-        <v>0.9030901873333845</v>
+        <v>0.9023953084964481</v>
       </c>
     </row>
     <row r="4">
@@ -581,33 +581,33 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>2.829558566575855</v>
+        <v>2.829558566575798</v>
       </c>
       <c r="H4" t="n">
-        <v>5.897459292430044</v>
+        <v>5.897459292430039</v>
       </c>
       <c r="I4" t="n">
-        <v>89.76512460309408</v>
+        <v>89.76510962162777</v>
       </c>
       <c r="J4" t="n">
-        <v>7.645550143864765</v>
+        <v>7.513329003516862</v>
       </c>
       <c r="K4" t="n">
-        <v>0.9025576237899711</v>
+        <v>0.9018516087723667</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>-0.98133423630042</v>
+        <v>-0.9881842858468689</v>
       </c>
       <c r="B5" t="n">
-        <v>1.105470462499802</v>
+        <v>1.147634932324883</v>
       </c>
       <c r="C5" t="n">
-        <v>1.369303951140356</v>
+        <v>1.183790238028504</v>
       </c>
       <c r="D5" t="n">
-        <v>705.9241692952735</v>
+        <v>779.3233274136177</v>
       </c>
       <c r="E5" t="n">
         <v>4</v>
@@ -618,33 +618,33 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>3.747264497291497</v>
+        <v>3.206224269650008</v>
       </c>
       <c r="H5" t="n">
-        <v>5.067471482717012</v>
+        <v>5.873811846390021</v>
       </c>
       <c r="I5" t="n">
-        <v>90.39985645846278</v>
+        <v>89.65560004584962</v>
       </c>
       <c r="J5" t="n">
-        <v>6.308978039494022</v>
+        <v>7.585275892952789</v>
       </c>
       <c r="K5" t="n">
-        <v>0.9004522742792861</v>
+        <v>0.898763739787688</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>-0.9823306052616613</v>
+        <v>-0.98133423630042</v>
       </c>
       <c r="B6" t="n">
-        <v>0.9289872559292436</v>
+        <v>1.105470462499802</v>
       </c>
       <c r="C6" t="n">
-        <v>0.8988877742713781</v>
+        <v>1.369303951140356</v>
       </c>
       <c r="D6" t="n">
-        <v>1015.702448145895</v>
+        <v>705.9241692952735</v>
       </c>
       <c r="E6" t="n">
         <v>5</v>
@@ -655,33 +655,33 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>2.699120004101129</v>
+        <v>3.747264497291508</v>
       </c>
       <c r="H6" t="n">
-        <v>4.668149422396129</v>
+        <v>5.067471482717011</v>
       </c>
       <c r="I6" t="n">
-        <v>90.5607541698636</v>
+        <v>90.39985262243552</v>
       </c>
       <c r="J6" t="n">
-        <v>5.922758445777547</v>
+        <v>6.148057097071797</v>
       </c>
       <c r="K6" t="n">
-        <v>0.9001460070614099</v>
+        <v>0.8985832182140933</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>-0.9881842858468689</v>
+        <v>-0.9823306052616613</v>
       </c>
       <c r="B7" t="n">
-        <v>1.147634932324883</v>
+        <v>0.9289872559292436</v>
       </c>
       <c r="C7" t="n">
-        <v>1.183790238028504</v>
+        <v>0.8988877742713781</v>
       </c>
       <c r="D7" t="n">
-        <v>779.3233274136177</v>
+        <v>1015.702448145895</v>
       </c>
       <c r="E7" t="n">
         <v>6</v>
@@ -692,33 +692,33 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>3.20622426965001</v>
+        <v>2.699120004101111</v>
       </c>
       <c r="H7" t="n">
-        <v>5.873811846390026</v>
+        <v>4.668149422396124</v>
       </c>
       <c r="I7" t="n">
-        <v>89.65561914260337</v>
+        <v>90.56077671501814</v>
       </c>
       <c r="J7" t="n">
-        <v>7.716262405861235</v>
+        <v>5.751021662752048</v>
       </c>
       <c r="K7" t="n">
-        <v>0.8994523421227424</v>
+        <v>0.8978608363062656</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>-0.9779437557508321</v>
+        <v>-0.9753529106293825</v>
       </c>
       <c r="B8" t="n">
-        <v>1.034730357262841</v>
+        <v>1.121024007782774</v>
       </c>
       <c r="C8" t="n">
-        <v>1.112125828664981</v>
+        <v>1.464891022064805</v>
       </c>
       <c r="D8" t="n">
-        <v>819.3268378711589</v>
+        <v>660.6619359813295</v>
       </c>
       <c r="E8" t="n">
         <v>7</v>
@@ -729,33 +729,33 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>2.840062785113513</v>
+        <v>3.796557778379044</v>
       </c>
       <c r="H8" t="n">
-        <v>3.747907256253344</v>
+        <v>5.42621810723347</v>
       </c>
       <c r="I8" t="n">
-        <v>91.1673747434628</v>
+        <v>90.06757441015667</v>
       </c>
       <c r="J8" t="n">
-        <v>4.50137399483912</v>
+        <v>6.647340254345798</v>
       </c>
       <c r="K8" t="n">
-        <v>0.897140366848819</v>
+        <v>0.8940480823010662</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>-0.9753529106293825</v>
+        <v>-0.9779437557508321</v>
       </c>
       <c r="B9" t="n">
-        <v>1.121024007782774</v>
+        <v>1.034730357262841</v>
       </c>
       <c r="C9" t="n">
-        <v>1.464891022064805</v>
+        <v>1.112125828664981</v>
       </c>
       <c r="D9" t="n">
-        <v>660.6619359813295</v>
+        <v>819.3268378711589</v>
       </c>
       <c r="E9" t="n">
         <v>8</v>
@@ -766,19 +766,19 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>3.796557778379082</v>
+        <v>2.840062785113556</v>
       </c>
       <c r="H9" t="n">
-        <v>5.426218107233474</v>
+        <v>3.747907256253351</v>
       </c>
       <c r="I9" t="n">
-        <v>90.0675843031344</v>
+        <v>91.16739659197755</v>
       </c>
       <c r="J9" t="n">
-        <v>6.796441376870342</v>
+        <v>4.272865793738961</v>
       </c>
       <c r="K9" t="n">
-        <v>0.8955073396797743</v>
+        <v>0.8929098689845326</v>
       </c>
     </row>
     <row r="10">
@@ -803,33 +803,33 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>3.163171815034923</v>
+        <v>3.163171815034922</v>
       </c>
       <c r="H10" t="n">
-        <v>4.205589412116763</v>
+        <v>4.20558941211676</v>
       </c>
       <c r="I10" t="n">
-        <v>90.89747562682783</v>
+        <v>90.8974872927856</v>
       </c>
       <c r="J10" t="n">
-        <v>5.053048234033386</v>
+        <v>4.850611954098968</v>
       </c>
       <c r="K10" t="n">
-        <v>0.8953006956406104</v>
+        <v>0.8918928272919321</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>-0.9785128573232006</v>
+        <v>-0.9769674601801612</v>
       </c>
       <c r="B11" t="n">
-        <v>1.093271521061723</v>
+        <v>1.135957426920155</v>
       </c>
       <c r="C11" t="n">
-        <v>1.376626248242171</v>
+        <v>1.285756858578975</v>
       </c>
       <c r="D11" t="n">
-        <v>678.5717391946255</v>
+        <v>665.9886825131628</v>
       </c>
       <c r="E11" t="n">
         <v>10</v>
@@ -840,19 +840,19 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>3.595719681393603</v>
+        <v>3.156527371826327</v>
       </c>
       <c r="H11" t="n">
-        <v>4.81113365811927</v>
+        <v>5.702982121395989</v>
       </c>
       <c r="I11" t="n">
-        <v>90.47749704831578</v>
+        <v>89.74993664942699</v>
       </c>
       <c r="J11" t="n">
-        <v>5.868595983977621</v>
+        <v>7.141809198787176</v>
       </c>
       <c r="K11" t="n">
-        <v>0.893030612571645</v>
+        <v>0.8911216145861861</v>
       </c>
     </row>
   </sheetData>
